--- a/vorlagen/Schichtplaner-Vorlage.xlsx
+++ b/vorlagen/Schichtplaner-Vorlage.xlsx
@@ -12,13 +12,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Studios" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schichten" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mitarbeiter" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feste Schichten" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sondertage" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Einstellungen" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Fragen'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Studios'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Schichten'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Mitarbeiter'!$A$1:$T$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Mitarbeiter'!$A$1:$W$150</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Mitarbeiter'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Feste Schichten'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Sondertage'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Einstellungen'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -505,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:B20"/>
+  <dimension ref="B1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -568,57 +574,85 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Was NICHT hier hinein gehört</t>
+    <row r="11" ht="32" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>5.  „Feste Schichten“ (freiwillig) – wer immer oder an einem bestimmten Tag fest eingeplant ist. Der Planer setzt diese zuerst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>6.  „Sondertage“ (freiwillig) – Tage mit geschlossener Schicht oder mehr Personen (Event, Inventur, Heiligabend).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>•  Urlaub und Krankheit – das steht in StudioChat unter Abwesenheiten und wird automatisch berücksichtigt.</t>
+          <t>7.  „Einstellungen“ – Wunschfrist, Feiertage, höchstens Tage am Stück, höchstens Wunsch-frei-Tage.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>•  Wünsche für einzelne Tage – die tragen die Mitarbeiter jeden Monat selbst in StudioChat ein (mit Frist).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>•  Gesundheitsangaben, private Adressen, Telefonnummern – werden für den Plan nicht gebraucht.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Tipps</t>
+          <t>Feste Schichten, Sondertage und Einstellungen lassen sich auch später direkt im Planer in der App ändern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Was NICHT hier hinein gehört</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>•  Urlaub und Krankheit – das steht in StudioChat unter Abwesenheiten und wird automatisch berücksichtigt.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>•  Felder mit Auswahlliste: Zelle anklicken, rechts erscheint ein kleiner Pfeil.</t>
+          <t>•  Wünsche für einzelne Tage – die tragen die Mitarbeiter jeden Monat selbst in StudioChat ein (mit Frist).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
+          <t>•  Gesundheitsangaben, private Adressen, Telefonnummern – werden für den Plan nicht gebraucht.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Tipps</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>•  Felder mit Auswahlliste: Zelle anklicken, rechts erscheint ein kleiner Pfeil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
           <t>•  Nicht sicher? Lieber in „Bemerkung“ in eigenen Worten schreiben als eine Spalte leer lassen.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="3" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>•  Unbekanntes darf leer bleiben – der Planer fragt dann nach, statt etwas anzunehmen.</t>
         </is>
@@ -1888,7 +1922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T150"/>
+  <dimension ref="A1:W150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1910,7 +1944,10 @@
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="28" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2019,6 +2056,24 @@
       </c>
       <c r="T1" s="4" t="inlineStr">
         <is>
+          <t>Springt bei
+Ausfall ein?</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Erster
+Arbeitstag</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Letzter
+Arbeitstag</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
           <t>Bemerkung</t>
         </is>
       </c>
@@ -2109,6 +2164,13 @@
       </c>
       <c r="T2" s="10" t="inlineStr">
         <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="U2" s="10" t="inlineStr"/>
+      <c r="V2" s="10" t="inlineStr"/>
+      <c r="W2" s="10" t="inlineStr">
+        <is>
           <t>samstags nur alle zwei Wochen</t>
         </is>
       </c>
@@ -2194,6 +2256,17 @@
         </is>
       </c>
       <c r="T3" s="10" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="U3" s="10" t="inlineStr">
+        <is>
+          <t>01.11.2026</t>
+        </is>
+      </c>
+      <c r="V3" s="10" t="inlineStr"/>
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>nicht allein – immer mit Studioleitung</t>
         </is>
@@ -2220,6 +2293,9 @@
       <c r="R4" s="6" t="n"/>
       <c r="S4" s="6" t="n"/>
       <c r="T4" s="6" t="n"/>
+      <c r="U4" s="6" t="n"/>
+      <c r="V4" s="6" t="n"/>
+      <c r="W4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -2242,6 +2318,9 @@
       <c r="R5" s="6" t="n"/>
       <c r="S5" s="6" t="n"/>
       <c r="T5" s="6" t="n"/>
+      <c r="U5" s="6" t="n"/>
+      <c r="V5" s="6" t="n"/>
+      <c r="W5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -2264,6 +2343,9 @@
       <c r="R6" s="6" t="n"/>
       <c r="S6" s="6" t="n"/>
       <c r="T6" s="6" t="n"/>
+      <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
+      <c r="W6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -2286,6 +2368,9 @@
       <c r="R7" s="6" t="n"/>
       <c r="S7" s="6" t="n"/>
       <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -2308,6 +2393,9 @@
       <c r="R8" s="6" t="n"/>
       <c r="S8" s="6" t="n"/>
       <c r="T8" s="6" t="n"/>
+      <c r="U8" s="6" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -2330,6 +2418,9 @@
       <c r="R9" s="6" t="n"/>
       <c r="S9" s="6" t="n"/>
       <c r="T9" s="6" t="n"/>
+      <c r="U9" s="6" t="n"/>
+      <c r="V9" s="6" t="n"/>
+      <c r="W9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -2352,6 +2443,9 @@
       <c r="R10" s="6" t="n"/>
       <c r="S10" s="6" t="n"/>
       <c r="T10" s="6" t="n"/>
+      <c r="U10" s="6" t="n"/>
+      <c r="V10" s="6" t="n"/>
+      <c r="W10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -2374,6 +2468,9 @@
       <c r="R11" s="6" t="n"/>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
+      <c r="U11" s="6" t="n"/>
+      <c r="V11" s="6" t="n"/>
+      <c r="W11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -2396,6 +2493,9 @@
       <c r="R12" s="6" t="n"/>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
+      <c r="U12" s="6" t="n"/>
+      <c r="V12" s="6" t="n"/>
+      <c r="W12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -2418,6 +2518,9 @@
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
+      <c r="U13" s="6" t="n"/>
+      <c r="V13" s="6" t="n"/>
+      <c r="W13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -2440,6 +2543,9 @@
       <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
+      <c r="U14" s="6" t="n"/>
+      <c r="V14" s="6" t="n"/>
+      <c r="W14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -2462,6 +2568,9 @@
       <c r="R15" s="6" t="n"/>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
+      <c r="U15" s="6" t="n"/>
+      <c r="V15" s="6" t="n"/>
+      <c r="W15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -2484,6 +2593,9 @@
       <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
+      <c r="U16" s="6" t="n"/>
+      <c r="V16" s="6" t="n"/>
+      <c r="W16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -2506,6 +2618,9 @@
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
+      <c r="U17" s="6" t="n"/>
+      <c r="V17" s="6" t="n"/>
+      <c r="W17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -2528,6 +2643,9 @@
       <c r="R18" s="6" t="n"/>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
+      <c r="U18" s="6" t="n"/>
+      <c r="V18" s="6" t="n"/>
+      <c r="W18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -2550,6 +2668,9 @@
       <c r="R19" s="6" t="n"/>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
+      <c r="U19" s="6" t="n"/>
+      <c r="V19" s="6" t="n"/>
+      <c r="W19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -2572,6 +2693,9 @@
       <c r="R20" s="6" t="n"/>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
+      <c r="U20" s="6" t="n"/>
+      <c r="V20" s="6" t="n"/>
+      <c r="W20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -2594,6 +2718,9 @@
       <c r="R21" s="6" t="n"/>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
+      <c r="U21" s="6" t="n"/>
+      <c r="V21" s="6" t="n"/>
+      <c r="W21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -2616,6 +2743,9 @@
       <c r="R22" s="6" t="n"/>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
+      <c r="U22" s="6" t="n"/>
+      <c r="V22" s="6" t="n"/>
+      <c r="W22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -2638,6 +2768,9 @@
       <c r="R23" s="6" t="n"/>
       <c r="S23" s="6" t="n"/>
       <c r="T23" s="6" t="n"/>
+      <c r="U23" s="6" t="n"/>
+      <c r="V23" s="6" t="n"/>
+      <c r="W23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -2660,6 +2793,9 @@
       <c r="R24" s="6" t="n"/>
       <c r="S24" s="6" t="n"/>
       <c r="T24" s="6" t="n"/>
+      <c r="U24" s="6" t="n"/>
+      <c r="V24" s="6" t="n"/>
+      <c r="W24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -2682,6 +2818,9 @@
       <c r="R25" s="6" t="n"/>
       <c r="S25" s="6" t="n"/>
       <c r="T25" s="6" t="n"/>
+      <c r="U25" s="6" t="n"/>
+      <c r="V25" s="6" t="n"/>
+      <c r="W25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -2704,6 +2843,9 @@
       <c r="R26" s="6" t="n"/>
       <c r="S26" s="6" t="n"/>
       <c r="T26" s="6" t="n"/>
+      <c r="U26" s="6" t="n"/>
+      <c r="V26" s="6" t="n"/>
+      <c r="W26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -2726,6 +2868,9 @@
       <c r="R27" s="6" t="n"/>
       <c r="S27" s="6" t="n"/>
       <c r="T27" s="6" t="n"/>
+      <c r="U27" s="6" t="n"/>
+      <c r="V27" s="6" t="n"/>
+      <c r="W27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -2748,6 +2893,9 @@
       <c r="R28" s="6" t="n"/>
       <c r="S28" s="6" t="n"/>
       <c r="T28" s="6" t="n"/>
+      <c r="U28" s="6" t="n"/>
+      <c r="V28" s="6" t="n"/>
+      <c r="W28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -2770,6 +2918,9 @@
       <c r="R29" s="6" t="n"/>
       <c r="S29" s="6" t="n"/>
       <c r="T29" s="6" t="n"/>
+      <c r="U29" s="6" t="n"/>
+      <c r="V29" s="6" t="n"/>
+      <c r="W29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -2792,6 +2943,9 @@
       <c r="R30" s="6" t="n"/>
       <c r="S30" s="6" t="n"/>
       <c r="T30" s="6" t="n"/>
+      <c r="U30" s="6" t="n"/>
+      <c r="V30" s="6" t="n"/>
+      <c r="W30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -2814,6 +2968,9 @@
       <c r="R31" s="6" t="n"/>
       <c r="S31" s="6" t="n"/>
       <c r="T31" s="6" t="n"/>
+      <c r="U31" s="6" t="n"/>
+      <c r="V31" s="6" t="n"/>
+      <c r="W31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -2836,6 +2993,9 @@
       <c r="R32" s="6" t="n"/>
       <c r="S32" s="6" t="n"/>
       <c r="T32" s="6" t="n"/>
+      <c r="U32" s="6" t="n"/>
+      <c r="V32" s="6" t="n"/>
+      <c r="W32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -2858,6 +3018,9 @@
       <c r="R33" s="6" t="n"/>
       <c r="S33" s="6" t="n"/>
       <c r="T33" s="6" t="n"/>
+      <c r="U33" s="6" t="n"/>
+      <c r="V33" s="6" t="n"/>
+      <c r="W33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -2880,6 +3043,9 @@
       <c r="R34" s="6" t="n"/>
       <c r="S34" s="6" t="n"/>
       <c r="T34" s="6" t="n"/>
+      <c r="U34" s="6" t="n"/>
+      <c r="V34" s="6" t="n"/>
+      <c r="W34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -2902,6 +3068,9 @@
       <c r="R35" s="6" t="n"/>
       <c r="S35" s="6" t="n"/>
       <c r="T35" s="6" t="n"/>
+      <c r="U35" s="6" t="n"/>
+      <c r="V35" s="6" t="n"/>
+      <c r="W35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -2924,6 +3093,9 @@
       <c r="R36" s="6" t="n"/>
       <c r="S36" s="6" t="n"/>
       <c r="T36" s="6" t="n"/>
+      <c r="U36" s="6" t="n"/>
+      <c r="V36" s="6" t="n"/>
+      <c r="W36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -2946,6 +3118,9 @@
       <c r="R37" s="6" t="n"/>
       <c r="S37" s="6" t="n"/>
       <c r="T37" s="6" t="n"/>
+      <c r="U37" s="6" t="n"/>
+      <c r="V37" s="6" t="n"/>
+      <c r="W37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -2968,6 +3143,9 @@
       <c r="R38" s="6" t="n"/>
       <c r="S38" s="6" t="n"/>
       <c r="T38" s="6" t="n"/>
+      <c r="U38" s="6" t="n"/>
+      <c r="V38" s="6" t="n"/>
+      <c r="W38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -2990,6 +3168,9 @@
       <c r="R39" s="6" t="n"/>
       <c r="S39" s="6" t="n"/>
       <c r="T39" s="6" t="n"/>
+      <c r="U39" s="6" t="n"/>
+      <c r="V39" s="6" t="n"/>
+      <c r="W39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -3012,6 +3193,9 @@
       <c r="R40" s="6" t="n"/>
       <c r="S40" s="6" t="n"/>
       <c r="T40" s="6" t="n"/>
+      <c r="U40" s="6" t="n"/>
+      <c r="V40" s="6" t="n"/>
+      <c r="W40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -3034,6 +3218,9 @@
       <c r="R41" s="6" t="n"/>
       <c r="S41" s="6" t="n"/>
       <c r="T41" s="6" t="n"/>
+      <c r="U41" s="6" t="n"/>
+      <c r="V41" s="6" t="n"/>
+      <c r="W41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -3056,6 +3243,9 @@
       <c r="R42" s="6" t="n"/>
       <c r="S42" s="6" t="n"/>
       <c r="T42" s="6" t="n"/>
+      <c r="U42" s="6" t="n"/>
+      <c r="V42" s="6" t="n"/>
+      <c r="W42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -3078,6 +3268,9 @@
       <c r="R43" s="6" t="n"/>
       <c r="S43" s="6" t="n"/>
       <c r="T43" s="6" t="n"/>
+      <c r="U43" s="6" t="n"/>
+      <c r="V43" s="6" t="n"/>
+      <c r="W43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -3100,6 +3293,9 @@
       <c r="R44" s="6" t="n"/>
       <c r="S44" s="6" t="n"/>
       <c r="T44" s="6" t="n"/>
+      <c r="U44" s="6" t="n"/>
+      <c r="V44" s="6" t="n"/>
+      <c r="W44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -3122,6 +3318,9 @@
       <c r="R45" s="6" t="n"/>
       <c r="S45" s="6" t="n"/>
       <c r="T45" s="6" t="n"/>
+      <c r="U45" s="6" t="n"/>
+      <c r="V45" s="6" t="n"/>
+      <c r="W45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -3144,6 +3343,9 @@
       <c r="R46" s="6" t="n"/>
       <c r="S46" s="6" t="n"/>
       <c r="T46" s="6" t="n"/>
+      <c r="U46" s="6" t="n"/>
+      <c r="V46" s="6" t="n"/>
+      <c r="W46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -3166,6 +3368,9 @@
       <c r="R47" s="6" t="n"/>
       <c r="S47" s="6" t="n"/>
       <c r="T47" s="6" t="n"/>
+      <c r="U47" s="6" t="n"/>
+      <c r="V47" s="6" t="n"/>
+      <c r="W47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -3188,6 +3393,9 @@
       <c r="R48" s="6" t="n"/>
       <c r="S48" s="6" t="n"/>
       <c r="T48" s="6" t="n"/>
+      <c r="U48" s="6" t="n"/>
+      <c r="V48" s="6" t="n"/>
+      <c r="W48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -3210,6 +3418,9 @@
       <c r="R49" s="6" t="n"/>
       <c r="S49" s="6" t="n"/>
       <c r="T49" s="6" t="n"/>
+      <c r="U49" s="6" t="n"/>
+      <c r="V49" s="6" t="n"/>
+      <c r="W49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -3232,6 +3443,9 @@
       <c r="R50" s="6" t="n"/>
       <c r="S50" s="6" t="n"/>
       <c r="T50" s="6" t="n"/>
+      <c r="U50" s="6" t="n"/>
+      <c r="V50" s="6" t="n"/>
+      <c r="W50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -3254,6 +3468,9 @@
       <c r="R51" s="6" t="n"/>
       <c r="S51" s="6" t="n"/>
       <c r="T51" s="6" t="n"/>
+      <c r="U51" s="6" t="n"/>
+      <c r="V51" s="6" t="n"/>
+      <c r="W51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -3276,6 +3493,9 @@
       <c r="R52" s="6" t="n"/>
       <c r="S52" s="6" t="n"/>
       <c r="T52" s="6" t="n"/>
+      <c r="U52" s="6" t="n"/>
+      <c r="V52" s="6" t="n"/>
+      <c r="W52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -3298,6 +3518,9 @@
       <c r="R53" s="6" t="n"/>
       <c r="S53" s="6" t="n"/>
       <c r="T53" s="6" t="n"/>
+      <c r="U53" s="6" t="n"/>
+      <c r="V53" s="6" t="n"/>
+      <c r="W53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -3320,6 +3543,9 @@
       <c r="R54" s="6" t="n"/>
       <c r="S54" s="6" t="n"/>
       <c r="T54" s="6" t="n"/>
+      <c r="U54" s="6" t="n"/>
+      <c r="V54" s="6" t="n"/>
+      <c r="W54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -3342,6 +3568,9 @@
       <c r="R55" s="6" t="n"/>
       <c r="S55" s="6" t="n"/>
       <c r="T55" s="6" t="n"/>
+      <c r="U55" s="6" t="n"/>
+      <c r="V55" s="6" t="n"/>
+      <c r="W55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -3364,6 +3593,9 @@
       <c r="R56" s="6" t="n"/>
       <c r="S56" s="6" t="n"/>
       <c r="T56" s="6" t="n"/>
+      <c r="U56" s="6" t="n"/>
+      <c r="V56" s="6" t="n"/>
+      <c r="W56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -3386,6 +3618,9 @@
       <c r="R57" s="6" t="n"/>
       <c r="S57" s="6" t="n"/>
       <c r="T57" s="6" t="n"/>
+      <c r="U57" s="6" t="n"/>
+      <c r="V57" s="6" t="n"/>
+      <c r="W57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -3408,6 +3643,9 @@
       <c r="R58" s="6" t="n"/>
       <c r="S58" s="6" t="n"/>
       <c r="T58" s="6" t="n"/>
+      <c r="U58" s="6" t="n"/>
+      <c r="V58" s="6" t="n"/>
+      <c r="W58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -3430,6 +3668,9 @@
       <c r="R59" s="6" t="n"/>
       <c r="S59" s="6" t="n"/>
       <c r="T59" s="6" t="n"/>
+      <c r="U59" s="6" t="n"/>
+      <c r="V59" s="6" t="n"/>
+      <c r="W59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -3452,6 +3693,9 @@
       <c r="R60" s="6" t="n"/>
       <c r="S60" s="6" t="n"/>
       <c r="T60" s="6" t="n"/>
+      <c r="U60" s="6" t="n"/>
+      <c r="V60" s="6" t="n"/>
+      <c r="W60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n"/>
@@ -3474,6 +3718,9 @@
       <c r="R61" s="6" t="n"/>
       <c r="S61" s="6" t="n"/>
       <c r="T61" s="6" t="n"/>
+      <c r="U61" s="6" t="n"/>
+      <c r="V61" s="6" t="n"/>
+      <c r="W61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n"/>
@@ -3496,6 +3743,9 @@
       <c r="R62" s="6" t="n"/>
       <c r="S62" s="6" t="n"/>
       <c r="T62" s="6" t="n"/>
+      <c r="U62" s="6" t="n"/>
+      <c r="V62" s="6" t="n"/>
+      <c r="W62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n"/>
@@ -3518,6 +3768,9 @@
       <c r="R63" s="6" t="n"/>
       <c r="S63" s="6" t="n"/>
       <c r="T63" s="6" t="n"/>
+      <c r="U63" s="6" t="n"/>
+      <c r="V63" s="6" t="n"/>
+      <c r="W63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -3540,6 +3793,9 @@
       <c r="R64" s="6" t="n"/>
       <c r="S64" s="6" t="n"/>
       <c r="T64" s="6" t="n"/>
+      <c r="U64" s="6" t="n"/>
+      <c r="V64" s="6" t="n"/>
+      <c r="W64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n"/>
@@ -3562,6 +3818,9 @@
       <c r="R65" s="6" t="n"/>
       <c r="S65" s="6" t="n"/>
       <c r="T65" s="6" t="n"/>
+      <c r="U65" s="6" t="n"/>
+      <c r="V65" s="6" t="n"/>
+      <c r="W65" s="6" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n"/>
@@ -3584,6 +3843,9 @@
       <c r="R66" s="6" t="n"/>
       <c r="S66" s="6" t="n"/>
       <c r="T66" s="6" t="n"/>
+      <c r="U66" s="6" t="n"/>
+      <c r="V66" s="6" t="n"/>
+      <c r="W66" s="6" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n"/>
@@ -3606,6 +3868,9 @@
       <c r="R67" s="6" t="n"/>
       <c r="S67" s="6" t="n"/>
       <c r="T67" s="6" t="n"/>
+      <c r="U67" s="6" t="n"/>
+      <c r="V67" s="6" t="n"/>
+      <c r="W67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -3628,6 +3893,9 @@
       <c r="R68" s="6" t="n"/>
       <c r="S68" s="6" t="n"/>
       <c r="T68" s="6" t="n"/>
+      <c r="U68" s="6" t="n"/>
+      <c r="V68" s="6" t="n"/>
+      <c r="W68" s="6" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n"/>
@@ -3650,6 +3918,9 @@
       <c r="R69" s="6" t="n"/>
       <c r="S69" s="6" t="n"/>
       <c r="T69" s="6" t="n"/>
+      <c r="U69" s="6" t="n"/>
+      <c r="V69" s="6" t="n"/>
+      <c r="W69" s="6" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n"/>
@@ -3672,6 +3943,9 @@
       <c r="R70" s="6" t="n"/>
       <c r="S70" s="6" t="n"/>
       <c r="T70" s="6" t="n"/>
+      <c r="U70" s="6" t="n"/>
+      <c r="V70" s="6" t="n"/>
+      <c r="W70" s="6" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n"/>
@@ -3694,6 +3968,9 @@
       <c r="R71" s="6" t="n"/>
       <c r="S71" s="6" t="n"/>
       <c r="T71" s="6" t="n"/>
+      <c r="U71" s="6" t="n"/>
+      <c r="V71" s="6" t="n"/>
+      <c r="W71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -3716,6 +3993,9 @@
       <c r="R72" s="6" t="n"/>
       <c r="S72" s="6" t="n"/>
       <c r="T72" s="6" t="n"/>
+      <c r="U72" s="6" t="n"/>
+      <c r="V72" s="6" t="n"/>
+      <c r="W72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n"/>
@@ -3738,6 +4018,9 @@
       <c r="R73" s="6" t="n"/>
       <c r="S73" s="6" t="n"/>
       <c r="T73" s="6" t="n"/>
+      <c r="U73" s="6" t="n"/>
+      <c r="V73" s="6" t="n"/>
+      <c r="W73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n"/>
@@ -3760,6 +4043,9 @@
       <c r="R74" s="6" t="n"/>
       <c r="S74" s="6" t="n"/>
       <c r="T74" s="6" t="n"/>
+      <c r="U74" s="6" t="n"/>
+      <c r="V74" s="6" t="n"/>
+      <c r="W74" s="6" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n"/>
@@ -3782,6 +4068,9 @@
       <c r="R75" s="6" t="n"/>
       <c r="S75" s="6" t="n"/>
       <c r="T75" s="6" t="n"/>
+      <c r="U75" s="6" t="n"/>
+      <c r="V75" s="6" t="n"/>
+      <c r="W75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -3804,6 +4093,9 @@
       <c r="R76" s="6" t="n"/>
       <c r="S76" s="6" t="n"/>
       <c r="T76" s="6" t="n"/>
+      <c r="U76" s="6" t="n"/>
+      <c r="V76" s="6" t="n"/>
+      <c r="W76" s="6" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n"/>
@@ -3826,6 +4118,9 @@
       <c r="R77" s="6" t="n"/>
       <c r="S77" s="6" t="n"/>
       <c r="T77" s="6" t="n"/>
+      <c r="U77" s="6" t="n"/>
+      <c r="V77" s="6" t="n"/>
+      <c r="W77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n"/>
@@ -3848,6 +4143,9 @@
       <c r="R78" s="6" t="n"/>
       <c r="S78" s="6" t="n"/>
       <c r="T78" s="6" t="n"/>
+      <c r="U78" s="6" t="n"/>
+      <c r="V78" s="6" t="n"/>
+      <c r="W78" s="6" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n"/>
@@ -3870,6 +4168,9 @@
       <c r="R79" s="6" t="n"/>
       <c r="S79" s="6" t="n"/>
       <c r="T79" s="6" t="n"/>
+      <c r="U79" s="6" t="n"/>
+      <c r="V79" s="6" t="n"/>
+      <c r="W79" s="6" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -3892,6 +4193,9 @@
       <c r="R80" s="6" t="n"/>
       <c r="S80" s="6" t="n"/>
       <c r="T80" s="6" t="n"/>
+      <c r="U80" s="6" t="n"/>
+      <c r="V80" s="6" t="n"/>
+      <c r="W80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n"/>
@@ -3914,6 +4218,9 @@
       <c r="R81" s="6" t="n"/>
       <c r="S81" s="6" t="n"/>
       <c r="T81" s="6" t="n"/>
+      <c r="U81" s="6" t="n"/>
+      <c r="V81" s="6" t="n"/>
+      <c r="W81" s="6" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n"/>
@@ -3936,6 +4243,9 @@
       <c r="R82" s="6" t="n"/>
       <c r="S82" s="6" t="n"/>
       <c r="T82" s="6" t="n"/>
+      <c r="U82" s="6" t="n"/>
+      <c r="V82" s="6" t="n"/>
+      <c r="W82" s="6" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n"/>
@@ -3958,6 +4268,9 @@
       <c r="R83" s="6" t="n"/>
       <c r="S83" s="6" t="n"/>
       <c r="T83" s="6" t="n"/>
+      <c r="U83" s="6" t="n"/>
+      <c r="V83" s="6" t="n"/>
+      <c r="W83" s="6" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -3980,6 +4293,9 @@
       <c r="R84" s="6" t="n"/>
       <c r="S84" s="6" t="n"/>
       <c r="T84" s="6" t="n"/>
+      <c r="U84" s="6" t="n"/>
+      <c r="V84" s="6" t="n"/>
+      <c r="W84" s="6" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n"/>
@@ -4002,6 +4318,9 @@
       <c r="R85" s="6" t="n"/>
       <c r="S85" s="6" t="n"/>
       <c r="T85" s="6" t="n"/>
+      <c r="U85" s="6" t="n"/>
+      <c r="V85" s="6" t="n"/>
+      <c r="W85" s="6" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n"/>
@@ -4024,6 +4343,9 @@
       <c r="R86" s="6" t="n"/>
       <c r="S86" s="6" t="n"/>
       <c r="T86" s="6" t="n"/>
+      <c r="U86" s="6" t="n"/>
+      <c r="V86" s="6" t="n"/>
+      <c r="W86" s="6" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n"/>
@@ -4046,6 +4368,9 @@
       <c r="R87" s="6" t="n"/>
       <c r="S87" s="6" t="n"/>
       <c r="T87" s="6" t="n"/>
+      <c r="U87" s="6" t="n"/>
+      <c r="V87" s="6" t="n"/>
+      <c r="W87" s="6" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n"/>
@@ -4068,6 +4393,9 @@
       <c r="R88" s="6" t="n"/>
       <c r="S88" s="6" t="n"/>
       <c r="T88" s="6" t="n"/>
+      <c r="U88" s="6" t="n"/>
+      <c r="V88" s="6" t="n"/>
+      <c r="W88" s="6" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n"/>
@@ -4090,6 +4418,9 @@
       <c r="R89" s="6" t="n"/>
       <c r="S89" s="6" t="n"/>
       <c r="T89" s="6" t="n"/>
+      <c r="U89" s="6" t="n"/>
+      <c r="V89" s="6" t="n"/>
+      <c r="W89" s="6" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n"/>
@@ -4112,6 +4443,9 @@
       <c r="R90" s="6" t="n"/>
       <c r="S90" s="6" t="n"/>
       <c r="T90" s="6" t="n"/>
+      <c r="U90" s="6" t="n"/>
+      <c r="V90" s="6" t="n"/>
+      <c r="W90" s="6" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n"/>
@@ -4134,6 +4468,9 @@
       <c r="R91" s="6" t="n"/>
       <c r="S91" s="6" t="n"/>
       <c r="T91" s="6" t="n"/>
+      <c r="U91" s="6" t="n"/>
+      <c r="V91" s="6" t="n"/>
+      <c r="W91" s="6" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n"/>
@@ -4156,6 +4493,9 @@
       <c r="R92" s="6" t="n"/>
       <c r="S92" s="6" t="n"/>
       <c r="T92" s="6" t="n"/>
+      <c r="U92" s="6" t="n"/>
+      <c r="V92" s="6" t="n"/>
+      <c r="W92" s="6" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n"/>
@@ -4178,6 +4518,9 @@
       <c r="R93" s="6" t="n"/>
       <c r="S93" s="6" t="n"/>
       <c r="T93" s="6" t="n"/>
+      <c r="U93" s="6" t="n"/>
+      <c r="V93" s="6" t="n"/>
+      <c r="W93" s="6" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n"/>
@@ -4200,6 +4543,9 @@
       <c r="R94" s="6" t="n"/>
       <c r="S94" s="6" t="n"/>
       <c r="T94" s="6" t="n"/>
+      <c r="U94" s="6" t="n"/>
+      <c r="V94" s="6" t="n"/>
+      <c r="W94" s="6" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n"/>
@@ -4222,6 +4568,9 @@
       <c r="R95" s="6" t="n"/>
       <c r="S95" s="6" t="n"/>
       <c r="T95" s="6" t="n"/>
+      <c r="U95" s="6" t="n"/>
+      <c r="V95" s="6" t="n"/>
+      <c r="W95" s="6" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n"/>
@@ -4244,6 +4593,9 @@
       <c r="R96" s="6" t="n"/>
       <c r="S96" s="6" t="n"/>
       <c r="T96" s="6" t="n"/>
+      <c r="U96" s="6" t="n"/>
+      <c r="V96" s="6" t="n"/>
+      <c r="W96" s="6" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n"/>
@@ -4266,6 +4618,9 @@
       <c r="R97" s="6" t="n"/>
       <c r="S97" s="6" t="n"/>
       <c r="T97" s="6" t="n"/>
+      <c r="U97" s="6" t="n"/>
+      <c r="V97" s="6" t="n"/>
+      <c r="W97" s="6" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n"/>
@@ -4288,6 +4643,9 @@
       <c r="R98" s="6" t="n"/>
       <c r="S98" s="6" t="n"/>
       <c r="T98" s="6" t="n"/>
+      <c r="U98" s="6" t="n"/>
+      <c r="V98" s="6" t="n"/>
+      <c r="W98" s="6" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n"/>
@@ -4310,6 +4668,9 @@
       <c r="R99" s="6" t="n"/>
       <c r="S99" s="6" t="n"/>
       <c r="T99" s="6" t="n"/>
+      <c r="U99" s="6" t="n"/>
+      <c r="V99" s="6" t="n"/>
+      <c r="W99" s="6" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n"/>
@@ -4332,6 +4693,9 @@
       <c r="R100" s="6" t="n"/>
       <c r="S100" s="6" t="n"/>
       <c r="T100" s="6" t="n"/>
+      <c r="U100" s="6" t="n"/>
+      <c r="V100" s="6" t="n"/>
+      <c r="W100" s="6" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n"/>
@@ -4354,6 +4718,9 @@
       <c r="R101" s="6" t="n"/>
       <c r="S101" s="6" t="n"/>
       <c r="T101" s="6" t="n"/>
+      <c r="U101" s="6" t="n"/>
+      <c r="V101" s="6" t="n"/>
+      <c r="W101" s="6" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n"/>
@@ -4376,6 +4743,9 @@
       <c r="R102" s="6" t="n"/>
       <c r="S102" s="6" t="n"/>
       <c r="T102" s="6" t="n"/>
+      <c r="U102" s="6" t="n"/>
+      <c r="V102" s="6" t="n"/>
+      <c r="W102" s="6" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n"/>
@@ -4398,6 +4768,9 @@
       <c r="R103" s="6" t="n"/>
       <c r="S103" s="6" t="n"/>
       <c r="T103" s="6" t="n"/>
+      <c r="U103" s="6" t="n"/>
+      <c r="V103" s="6" t="n"/>
+      <c r="W103" s="6" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n"/>
@@ -4420,6 +4793,9 @@
       <c r="R104" s="6" t="n"/>
       <c r="S104" s="6" t="n"/>
       <c r="T104" s="6" t="n"/>
+      <c r="U104" s="6" t="n"/>
+      <c r="V104" s="6" t="n"/>
+      <c r="W104" s="6" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n"/>
@@ -4442,6 +4818,9 @@
       <c r="R105" s="6" t="n"/>
       <c r="S105" s="6" t="n"/>
       <c r="T105" s="6" t="n"/>
+      <c r="U105" s="6" t="n"/>
+      <c r="V105" s="6" t="n"/>
+      <c r="W105" s="6" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n"/>
@@ -4464,6 +4843,9 @@
       <c r="R106" s="6" t="n"/>
       <c r="S106" s="6" t="n"/>
       <c r="T106" s="6" t="n"/>
+      <c r="U106" s="6" t="n"/>
+      <c r="V106" s="6" t="n"/>
+      <c r="W106" s="6" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n"/>
@@ -4486,6 +4868,9 @@
       <c r="R107" s="6" t="n"/>
       <c r="S107" s="6" t="n"/>
       <c r="T107" s="6" t="n"/>
+      <c r="U107" s="6" t="n"/>
+      <c r="V107" s="6" t="n"/>
+      <c r="W107" s="6" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n"/>
@@ -4508,6 +4893,9 @@
       <c r="R108" s="6" t="n"/>
       <c r="S108" s="6" t="n"/>
       <c r="T108" s="6" t="n"/>
+      <c r="U108" s="6" t="n"/>
+      <c r="V108" s="6" t="n"/>
+      <c r="W108" s="6" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n"/>
@@ -4530,6 +4918,9 @@
       <c r="R109" s="6" t="n"/>
       <c r="S109" s="6" t="n"/>
       <c r="T109" s="6" t="n"/>
+      <c r="U109" s="6" t="n"/>
+      <c r="V109" s="6" t="n"/>
+      <c r="W109" s="6" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n"/>
@@ -4552,6 +4943,9 @@
       <c r="R110" s="6" t="n"/>
       <c r="S110" s="6" t="n"/>
       <c r="T110" s="6" t="n"/>
+      <c r="U110" s="6" t="n"/>
+      <c r="V110" s="6" t="n"/>
+      <c r="W110" s="6" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n"/>
@@ -4574,6 +4968,9 @@
       <c r="R111" s="6" t="n"/>
       <c r="S111" s="6" t="n"/>
       <c r="T111" s="6" t="n"/>
+      <c r="U111" s="6" t="n"/>
+      <c r="V111" s="6" t="n"/>
+      <c r="W111" s="6" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="n"/>
@@ -4596,6 +4993,9 @@
       <c r="R112" s="6" t="n"/>
       <c r="S112" s="6" t="n"/>
       <c r="T112" s="6" t="n"/>
+      <c r="U112" s="6" t="n"/>
+      <c r="V112" s="6" t="n"/>
+      <c r="W112" s="6" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n"/>
@@ -4618,6 +5018,9 @@
       <c r="R113" s="6" t="n"/>
       <c r="S113" s="6" t="n"/>
       <c r="T113" s="6" t="n"/>
+      <c r="U113" s="6" t="n"/>
+      <c r="V113" s="6" t="n"/>
+      <c r="W113" s="6" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="n"/>
@@ -4640,6 +5043,9 @@
       <c r="R114" s="6" t="n"/>
       <c r="S114" s="6" t="n"/>
       <c r="T114" s="6" t="n"/>
+      <c r="U114" s="6" t="n"/>
+      <c r="V114" s="6" t="n"/>
+      <c r="W114" s="6" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n"/>
@@ -4662,6 +5068,9 @@
       <c r="R115" s="6" t="n"/>
       <c r="S115" s="6" t="n"/>
       <c r="T115" s="6" t="n"/>
+      <c r="U115" s="6" t="n"/>
+      <c r="V115" s="6" t="n"/>
+      <c r="W115" s="6" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n"/>
@@ -4684,6 +5093,9 @@
       <c r="R116" s="6" t="n"/>
       <c r="S116" s="6" t="n"/>
       <c r="T116" s="6" t="n"/>
+      <c r="U116" s="6" t="n"/>
+      <c r="V116" s="6" t="n"/>
+      <c r="W116" s="6" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n"/>
@@ -4706,6 +5118,9 @@
       <c r="R117" s="6" t="n"/>
       <c r="S117" s="6" t="n"/>
       <c r="T117" s="6" t="n"/>
+      <c r="U117" s="6" t="n"/>
+      <c r="V117" s="6" t="n"/>
+      <c r="W117" s="6" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n"/>
@@ -4728,6 +5143,9 @@
       <c r="R118" s="6" t="n"/>
       <c r="S118" s="6" t="n"/>
       <c r="T118" s="6" t="n"/>
+      <c r="U118" s="6" t="n"/>
+      <c r="V118" s="6" t="n"/>
+      <c r="W118" s="6" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="n"/>
@@ -4750,6 +5168,9 @@
       <c r="R119" s="6" t="n"/>
       <c r="S119" s="6" t="n"/>
       <c r="T119" s="6" t="n"/>
+      <c r="U119" s="6" t="n"/>
+      <c r="V119" s="6" t="n"/>
+      <c r="W119" s="6" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="n"/>
@@ -4772,6 +5193,9 @@
       <c r="R120" s="6" t="n"/>
       <c r="S120" s="6" t="n"/>
       <c r="T120" s="6" t="n"/>
+      <c r="U120" s="6" t="n"/>
+      <c r="V120" s="6" t="n"/>
+      <c r="W120" s="6" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="n"/>
@@ -4794,6 +5218,9 @@
       <c r="R121" s="6" t="n"/>
       <c r="S121" s="6" t="n"/>
       <c r="T121" s="6" t="n"/>
+      <c r="U121" s="6" t="n"/>
+      <c r="V121" s="6" t="n"/>
+      <c r="W121" s="6" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="n"/>
@@ -4816,6 +5243,9 @@
       <c r="R122" s="6" t="n"/>
       <c r="S122" s="6" t="n"/>
       <c r="T122" s="6" t="n"/>
+      <c r="U122" s="6" t="n"/>
+      <c r="V122" s="6" t="n"/>
+      <c r="W122" s="6" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="n"/>
@@ -4838,6 +5268,9 @@
       <c r="R123" s="6" t="n"/>
       <c r="S123" s="6" t="n"/>
       <c r="T123" s="6" t="n"/>
+      <c r="U123" s="6" t="n"/>
+      <c r="V123" s="6" t="n"/>
+      <c r="W123" s="6" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="n"/>
@@ -4860,6 +5293,9 @@
       <c r="R124" s="6" t="n"/>
       <c r="S124" s="6" t="n"/>
       <c r="T124" s="6" t="n"/>
+      <c r="U124" s="6" t="n"/>
+      <c r="V124" s="6" t="n"/>
+      <c r="W124" s="6" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="n"/>
@@ -4882,6 +5318,9 @@
       <c r="R125" s="6" t="n"/>
       <c r="S125" s="6" t="n"/>
       <c r="T125" s="6" t="n"/>
+      <c r="U125" s="6" t="n"/>
+      <c r="V125" s="6" t="n"/>
+      <c r="W125" s="6" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="n"/>
@@ -4904,6 +5343,9 @@
       <c r="R126" s="6" t="n"/>
       <c r="S126" s="6" t="n"/>
       <c r="T126" s="6" t="n"/>
+      <c r="U126" s="6" t="n"/>
+      <c r="V126" s="6" t="n"/>
+      <c r="W126" s="6" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="n"/>
@@ -4926,6 +5368,9 @@
       <c r="R127" s="6" t="n"/>
       <c r="S127" s="6" t="n"/>
       <c r="T127" s="6" t="n"/>
+      <c r="U127" s="6" t="n"/>
+      <c r="V127" s="6" t="n"/>
+      <c r="W127" s="6" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="n"/>
@@ -4948,6 +5393,9 @@
       <c r="R128" s="6" t="n"/>
       <c r="S128" s="6" t="n"/>
       <c r="T128" s="6" t="n"/>
+      <c r="U128" s="6" t="n"/>
+      <c r="V128" s="6" t="n"/>
+      <c r="W128" s="6" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="n"/>
@@ -4970,6 +5418,9 @@
       <c r="R129" s="6" t="n"/>
       <c r="S129" s="6" t="n"/>
       <c r="T129" s="6" t="n"/>
+      <c r="U129" s="6" t="n"/>
+      <c r="V129" s="6" t="n"/>
+      <c r="W129" s="6" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="n"/>
@@ -4992,6 +5443,9 @@
       <c r="R130" s="6" t="n"/>
       <c r="S130" s="6" t="n"/>
       <c r="T130" s="6" t="n"/>
+      <c r="U130" s="6" t="n"/>
+      <c r="V130" s="6" t="n"/>
+      <c r="W130" s="6" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="n"/>
@@ -5014,6 +5468,9 @@
       <c r="R131" s="6" t="n"/>
       <c r="S131" s="6" t="n"/>
       <c r="T131" s="6" t="n"/>
+      <c r="U131" s="6" t="n"/>
+      <c r="V131" s="6" t="n"/>
+      <c r="W131" s="6" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="n"/>
@@ -5036,6 +5493,9 @@
       <c r="R132" s="6" t="n"/>
       <c r="S132" s="6" t="n"/>
       <c r="T132" s="6" t="n"/>
+      <c r="U132" s="6" t="n"/>
+      <c r="V132" s="6" t="n"/>
+      <c r="W132" s="6" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="n"/>
@@ -5058,6 +5518,9 @@
       <c r="R133" s="6" t="n"/>
       <c r="S133" s="6" t="n"/>
       <c r="T133" s="6" t="n"/>
+      <c r="U133" s="6" t="n"/>
+      <c r="V133" s="6" t="n"/>
+      <c r="W133" s="6" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="n"/>
@@ -5080,6 +5543,9 @@
       <c r="R134" s="6" t="n"/>
       <c r="S134" s="6" t="n"/>
       <c r="T134" s="6" t="n"/>
+      <c r="U134" s="6" t="n"/>
+      <c r="V134" s="6" t="n"/>
+      <c r="W134" s="6" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="n"/>
@@ -5102,6 +5568,9 @@
       <c r="R135" s="6" t="n"/>
       <c r="S135" s="6" t="n"/>
       <c r="T135" s="6" t="n"/>
+      <c r="U135" s="6" t="n"/>
+      <c r="V135" s="6" t="n"/>
+      <c r="W135" s="6" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="n"/>
@@ -5124,6 +5593,9 @@
       <c r="R136" s="6" t="n"/>
       <c r="S136" s="6" t="n"/>
       <c r="T136" s="6" t="n"/>
+      <c r="U136" s="6" t="n"/>
+      <c r="V136" s="6" t="n"/>
+      <c r="W136" s="6" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="n"/>
@@ -5146,6 +5618,9 @@
       <c r="R137" s="6" t="n"/>
       <c r="S137" s="6" t="n"/>
       <c r="T137" s="6" t="n"/>
+      <c r="U137" s="6" t="n"/>
+      <c r="V137" s="6" t="n"/>
+      <c r="W137" s="6" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="n"/>
@@ -5168,6 +5643,9 @@
       <c r="R138" s="6" t="n"/>
       <c r="S138" s="6" t="n"/>
       <c r="T138" s="6" t="n"/>
+      <c r="U138" s="6" t="n"/>
+      <c r="V138" s="6" t="n"/>
+      <c r="W138" s="6" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="n"/>
@@ -5190,6 +5668,9 @@
       <c r="R139" s="6" t="n"/>
       <c r="S139" s="6" t="n"/>
       <c r="T139" s="6" t="n"/>
+      <c r="U139" s="6" t="n"/>
+      <c r="V139" s="6" t="n"/>
+      <c r="W139" s="6" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="n"/>
@@ -5212,6 +5693,9 @@
       <c r="R140" s="6" t="n"/>
       <c r="S140" s="6" t="n"/>
       <c r="T140" s="6" t="n"/>
+      <c r="U140" s="6" t="n"/>
+      <c r="V140" s="6" t="n"/>
+      <c r="W140" s="6" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="n"/>
@@ -5234,6 +5718,9 @@
       <c r="R141" s="6" t="n"/>
       <c r="S141" s="6" t="n"/>
       <c r="T141" s="6" t="n"/>
+      <c r="U141" s="6" t="n"/>
+      <c r="V141" s="6" t="n"/>
+      <c r="W141" s="6" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="n"/>
@@ -5256,6 +5743,9 @@
       <c r="R142" s="6" t="n"/>
       <c r="S142" s="6" t="n"/>
       <c r="T142" s="6" t="n"/>
+      <c r="U142" s="6" t="n"/>
+      <c r="V142" s="6" t="n"/>
+      <c r="W142" s="6" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="n"/>
@@ -5278,6 +5768,9 @@
       <c r="R143" s="6" t="n"/>
       <c r="S143" s="6" t="n"/>
       <c r="T143" s="6" t="n"/>
+      <c r="U143" s="6" t="n"/>
+      <c r="V143" s="6" t="n"/>
+      <c r="W143" s="6" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="n"/>
@@ -5300,6 +5793,9 @@
       <c r="R144" s="6" t="n"/>
       <c r="S144" s="6" t="n"/>
       <c r="T144" s="6" t="n"/>
+      <c r="U144" s="6" t="n"/>
+      <c r="V144" s="6" t="n"/>
+      <c r="W144" s="6" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="n"/>
@@ -5322,6 +5818,9 @@
       <c r="R145" s="6" t="n"/>
       <c r="S145" s="6" t="n"/>
       <c r="T145" s="6" t="n"/>
+      <c r="U145" s="6" t="n"/>
+      <c r="V145" s="6" t="n"/>
+      <c r="W145" s="6" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="n"/>
@@ -5344,6 +5843,9 @@
       <c r="R146" s="6" t="n"/>
       <c r="S146" s="6" t="n"/>
       <c r="T146" s="6" t="n"/>
+      <c r="U146" s="6" t="n"/>
+      <c r="V146" s="6" t="n"/>
+      <c r="W146" s="6" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="n"/>
@@ -5366,6 +5868,9 @@
       <c r="R147" s="6" t="n"/>
       <c r="S147" s="6" t="n"/>
       <c r="T147" s="6" t="n"/>
+      <c r="U147" s="6" t="n"/>
+      <c r="V147" s="6" t="n"/>
+      <c r="W147" s="6" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="n"/>
@@ -5388,6 +5893,9 @@
       <c r="R148" s="6" t="n"/>
       <c r="S148" s="6" t="n"/>
       <c r="T148" s="6" t="n"/>
+      <c r="U148" s="6" t="n"/>
+      <c r="V148" s="6" t="n"/>
+      <c r="W148" s="6" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="n"/>
@@ -5410,6 +5918,9 @@
       <c r="R149" s="6" t="n"/>
       <c r="S149" s="6" t="n"/>
       <c r="T149" s="6" t="n"/>
+      <c r="U149" s="6" t="n"/>
+      <c r="V149" s="6" t="n"/>
+      <c r="W149" s="6" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="n"/>
@@ -5432,10 +5943,13 @@
       <c r="R150" s="6" t="n"/>
       <c r="S150" s="6" t="n"/>
       <c r="T150" s="6" t="n"/>
+      <c r="U150" s="6" t="n"/>
+      <c r="V150" s="6" t="n"/>
+      <c r="W150" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T150"/>
-  <dataValidations count="5">
+  <autoFilter ref="A1:W150"/>
+  <dataValidations count="6">
     <dataValidation sqref="B2:B150" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Bitte aus der Liste wählen" error="Rolle aus der Liste wählen" promptTitle="Auswahl" prompt="Rolle aus der Liste wählen" type="list" errorStyle="warning">
       <formula1>"Vollzeit,Teilzeit,Minijob,Duales Studium,Azubi,Werkstudent,Aushilfe,Studioleitung,Regionalleitung"</formula1>
     </dataValidation>
@@ -5451,6 +5965,1363 @@
     <dataValidation sqref="S2:S150" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Bitte aus der Liste wählen" error="Früh, Spät oder egal" promptTitle="Auswahl" prompt="Früh, Spät oder egal" type="list" errorStyle="stop">
       <formula1>"Früh,Spät,egal"</formula1>
     </dataValidation>
+    <dataValidation sqref="T2:T150" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Bitte aus der Liste wählen" error="ja = wird bei Krankheit anderer zuerst gefragt" promptTitle="Auswahl" prompt="ja = wird bei Krankheit anderer zuerst gefragt" type="list" errorStyle="stop">
+      <formula1>"ja,nein"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Person
+(Name wie im Blatt Mitarbeiter)</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Studio</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Schicht
+(Name wie im Blatt Schichten)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Wochentage ODER Datum</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Lisa M.</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Nippes</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Spät</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Mo, Mi</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>Beispiel – bitte anpassen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Tom K.</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Porz</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Früh</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>14.11.2026</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Beispiel – Einweisung neues Gerät</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n"/>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n"/>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n"/>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n"/>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n"/>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n"/>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n"/>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n"/>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n"/>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n"/>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n"/>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n"/>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n"/>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n"/>
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n"/>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n"/>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n"/>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Bitte aus der Liste wählen" error="Studio aus der Liste" promptTitle="Auswahl" prompt="Studio aus der Liste" type="list" errorStyle="stop">
+      <formula1>"Longerich,Nippes,Ebertplatz,Rath,Porz,Rondorf,Hürth,Brühl,Niederkassel Mondorf,Refrath,Overath,Marialinden,Rösrath,Seelscheid"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Datum
+(TT.MM.JJJJ)</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Studio
+(oder „alle“)</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Schicht
+(leer = alle)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Wie viele
+mehr?</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Anlass / Notiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>24.12.2026</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>alle</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>geschlossen</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Spät</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr"/>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Beispiel – Heiligabend nur bis 14 Uhr</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>07.11.2026</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Rath</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>mehr Personen</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Samstag</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Beispiel – Tag der offenen Tür</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n"/>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n"/>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n"/>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n"/>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n"/>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n"/>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n"/>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n"/>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n"/>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n"/>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n"/>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n"/>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n"/>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n"/>
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+      <c r="F57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n"/>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n"/>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n"/>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="6" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n"/>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n"/>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="6" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n"/>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n"/>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="6" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n"/>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="6" t="n"/>
+      <c r="F66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n"/>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="6" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n"/>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n"/>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="6" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n"/>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n"/>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n"/>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n"/>
+      <c r="F72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n"/>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n"/>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="6" t="n"/>
+      <c r="E74" s="6" t="n"/>
+      <c r="F74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n"/>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
+      <c r="E75" s="6" t="n"/>
+      <c r="F75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n"/>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n"/>
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="n"/>
+      <c r="E77" s="6" t="n"/>
+      <c r="F77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n"/>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+      <c r="F78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n"/>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="6" t="n"/>
+      <c r="F79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="n"/>
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n"/>
+      <c r="E80" s="6" t="n"/>
+      <c r="F80" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B80" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Bitte aus der Liste wählen" error="Studio aus der Liste oder „alle“" promptTitle="Auswahl" prompt="Studio aus der Liste oder „alle“" type="list" errorStyle="stop">
+      <formula1>"alle,Longerich,Nippes,Ebertplatz,Rath,Porz,Rondorf,Hürth,Brühl,Niederkassel Mondorf,Refrath,Overath,Marialinden,Rösrath,Seelscheid"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C80" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Bitte aus der Liste wählen" error="geschlossen = Schicht fällt weg · mehr Personen = Mindestbesetzung steigt" promptTitle="Auswahl" prompt="geschlossen = Schicht fällt weg · mehr Personen = Mindestbesetzung steigt" type="list" errorStyle="stop">
+      <formula1>"geschlossen,mehr Personen"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Einstellung</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Wert</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Erklärung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Wunschfrist (Tag im Vormonat)</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Bis zu diesem Tag tragen die Mitarbeiter ihre Wünsche für den Folgemonat ein.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Feiertage geschlossen?</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>ja = an NRW-Feiertagen wird niemand eingeplant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Höchstens Tage am Stück</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Mehr Tage hintereinander nur als sichtbare Rückfrage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Höchstens Wunsch-frei-Tage pro Person und Monat</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>0 = keine Grenze.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Bitte aus der Liste wählen" error="ja oder nein" promptTitle="Auswahl" prompt="ja oder nein" type="list" errorStyle="stop">
+      <formula1>"ja,nein"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/vorlagen/Schichtplaner-Vorlage.xlsx
+++ b/vorlagen/Schichtplaner-Vorlage.xlsx
@@ -61,13 +61,13 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
+      <i val="1"/>
+      <color rgb="0064748B"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="0064748B"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -136,14 +136,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -670,13 +673,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -697,6 +701,11 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
+          <t>Heute in der App</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
           <t>Antwort</t>
         </is>
       </c>
@@ -707,15 +716,20 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Studios und Öffnungszeiten</t>
+          <t>A · Ohne diese Angaben gibt es keinen Plan</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Welche Öffnungszeiten hat jedes der 14 Studios an welchem Wochentag? (Die Namen stehen schon im Excel – bitte prüfen.) Bitte im Excel im Blatt „Studios“ eintragen.</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="n"/>
+          <t>Welche Studios sollen im ersten Monat mitgeplant werden – alle 14 oder zum Testen erst eins oder zwei?</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Empfehlung: erst ein Studio.</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="5" t="n">
@@ -723,15 +737,20 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Studios und Öffnungszeiten</t>
+          <t>A · Ohne diese Angaben gibt es keinen Plan</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>An welchen Feiertagen sind die Studios zu? Gibt es Betriebsferien?</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="n"/>
+          <t>Öffnungszeiten je Studio und Wochentag.</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Ins Excel, Blatt „Studios“.</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n"/>
     </row>
     <row r="4" ht="48" customHeight="1">
       <c r="A4" s="5" t="n">
@@ -739,15 +758,20 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Schichten und Besetzung</t>
+          <t>A · Ohne diese Angaben gibt es keinen Plan</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Gibt es feste Schichten (z. B. Früh 7–14 Uhr, Spät 14–21 Uhr) oder wechselnde Zeiten? Sind sie in allen Studios gleich? Bitte im Excel im Blatt „Schichten“ eintragen.</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="n"/>
+          <t>Schichten je Studio: Name, Beginn, Ende, an welchen Wochentagen. Sind sie in allen Studios gleich?</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Ins Excel, Blatt „Schichten“. Heute in der Demo: Früh 7–14, Spät 14–21, Samstag 9–14.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -755,15 +779,20 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Schichten und Besetzung</t>
+          <t>A · Ohne diese Angaben gibt es keinen Plan</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Wie viele Leute müssen mindestens gleichzeitig im Studio sein? Gibt es Zeiten, Tage oder Studios, an denen es mehr sein müssen (Stoßzeiten)?</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="n"/>
+          <t>Das Team: eine Zeile pro Person – Name genau wie in der App, Hauptstudio, in welchen Studios sie aushilft, Stunden pro Woche (Minijob: Monatsgrenze).</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Ins Excel, Blatt „Mitarbeiter“.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="5" t="n">
@@ -771,15 +800,20 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Schichten und Besetzung</t>
+          <t>A · Ohne diese Angaben gibt es keinen Plan</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Wer darf nicht allein im Studio sein – nur Azubis und Neue, oder auch bestimmte Personen? Und wer zählt als „Begleitung“, damit diese Person nicht mehr allein ist?</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n"/>
+          <t>Wer kann wann grundsätzlich nicht? (z. B. „nie Dienstag“, „nur früh“, „Di Uni“)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Ins Excel, Blatt „Mitarbeiter“, Spalten Mo–So und „Sperrzeiten“.</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n"/>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -787,15 +821,20 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Schichten und Besetzung</t>
+          <t>B · Besetzung</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Gibt es Aufgaben, die nur bestimmte Personen können (z. B. Probetraining, Kasse, Abschluss am Abend, Erste Hilfe)? Muss in jeder Schicht mindestens eine solche Person da sein?</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n"/>
+          <t>Wie viele Personen müssen mindestens gleichzeitig im Studio sein?</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Heute: 1 je Schicht.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="5" t="n">
@@ -803,15 +842,20 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Schichten und Besetzung</t>
+          <t>B · Besetzung</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Werden Regionalleiter mit in den Plan eingeteilt, oder stehen sie nur bei Bedarf zur Verfügung?</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n"/>
+          <t>Gibt es Stoßzeiten, Tage oder Studios, an denen mehr Leute da sein müssen? Wann, wo, wie viele?</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Heute: nur über „Sondertage“ für einzelne Daten.</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="5" t="n">
@@ -819,15 +863,20 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Arbeitszeit und Fairness</t>
+          <t>B · Besetzung</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Wie lang darf eine Schicht höchstens sein, und ab wann gibt es Pause?</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n"/>
+          <t>Wer darf nicht allein im Studio sein (Azubis, Neue, bestimmte Personen)? Und wer zählt als Begleitung?</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Heute: Begleitung ist jede Person mit „darf allein: ja“.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="5" t="n">
@@ -835,15 +884,20 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Arbeitszeit und Fairness</t>
+          <t>B · Besetzung</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Wie viele Tage am Stück darf jemand höchstens arbeiten? Gibt es feste freie Tage?</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n"/>
+          <t>Muss in bestimmten Schichten jemand mit einer bestimmten Fähigkeit da sein (Probetraining, Kasse, Abschluss am Abend, Erste Hilfe)? In welchen?</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Heute: je Schicht eine Fähigkeit („Braucht jemanden mit …“).</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="5" t="n">
@@ -851,15 +905,20 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Arbeitszeit und Fairness</t>
+          <t>B · Besetzung</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Wie werden Wochenenden und Feiertage verteilt – reihum, oder hat jemand fest frei?</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n"/>
+          <t>Werden Studioleitungen und Regionalleiter fest eingeplant oder nur bei Bedarf?</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Heute: wie alle anderen, wenn sie im Blatt „Mitarbeiter“ stehen.</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n"/>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="5" t="n">
@@ -867,15 +926,20 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Arbeitszeit und Fairness</t>
+          <t>C · Arbeitszeit</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Gibt es Mitarbeiter unter 18 Jahren? Für sie gelten strengere Regeln (z. B. keine späten Schichten).</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n"/>
+          <t>Wie lang darf eine Schicht höchstens sein, und ab wann gibt es Pause?</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Heute: wird nicht geprüft.</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n"/>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="5" t="n">
@@ -883,15 +947,20 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Arbeitszeit und Fairness</t>
+          <t>C · Arbeitszeit</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Minijobs: Gilt pro Person eine feste Höchstzahl an Stunden im Monat? Wenn nein: Wie hoch ist der Stundenlohn, damit die Maschine die Grenze ausrechnen kann?</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n"/>
+          <t>Wie viele Tage am Stück darf jemand höchstens arbeiten?</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Heute: 6.</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n"/>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="5" t="n">
@@ -899,15 +968,20 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Wünsche und Konflikte</t>
+          <t>C · Arbeitszeit</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Was hat Vorrang, wenn sich etwas beisst? Bitte in eine Reihenfolge bringen: Besetzung · vereinbarte Stunden · Wünsche der Mitarbeiter · Fairness.</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n"/>
+          <t>Höchstens wie viele Tage pro Woche – für alle gleich oder je Person?</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Heute: je Person im Excel, sonst ohne Grenze.</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="5" t="n">
@@ -915,15 +989,20 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Wünsche und Konflikte</t>
+          <t>C · Arbeitszeit</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Bis wann vor dem Monat müssen die Wünsche eingetragen sein (z. B. bis zum 15. des Vormonats)?</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n"/>
+          <t>Gibt es Mitarbeiter unter 18?</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Wenn ja, gilt automatisch: nur 6–20 Uhr, höchstens 8 Stunden.</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n"/>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="5" t="n">
@@ -931,15 +1010,20 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Wünsche und Konflikte</t>
+          <t>C · Arbeitszeit</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Wie viele Wunsch-frei-Tage darf jeder pro Monat angeben?</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="n"/>
+          <t>Feiertage in NRW: geschlossen oder offen? Gibt es Betriebsferien?</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Heute: offen (umschaltbar).</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n"/>
     </row>
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="5" t="n">
@@ -947,15 +1031,20 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Wünsche und Konflikte</t>
+          <t>D · Wünsche und Fairness</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Wenn eine Schicht nicht zu besetzen ist: Soll die Maschine nur die Lücke melden oder gleich vorschlagen, wen man fragen könnte?</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n"/>
+          <t>Bis zum wievielten des Vormonats müssen Wünsche eingetragen sein?</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Heute: bis zum 15.</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="5" t="n">
@@ -963,15 +1052,20 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Ablauf und LogX</t>
+          <t>D · Wünsche und Fairness</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Wer prüft und veröffentlicht den Plan – nur Sie, oder auch die Studioleiter für ihre Studios?</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="n"/>
+          <t>Wie viele Wunsch-frei-Tage darf jede Person im Monat angeben?</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Heute: keine Grenze.</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n"/>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="5" t="n">
@@ -979,15 +1073,20 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Ablauf und LogX</t>
+          <t>D · Wünsche und Fairness</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Wie weit im Voraus soll der Plan fertig sein (z. B. am 20. für den nächsten Monat)?</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n"/>
+          <t>Was hat Vorrang, wenn es sich beisst? Bitte in eine Reihenfolge: Besetzung · vereinbarte Stunden · Wünsche · Fairness.</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Heute: Besetzung zuerst; ein Wunsch wird nur als Rückfrage gebrochen.</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n"/>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="5" t="n">
@@ -995,15 +1094,20 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Ablauf und LogX</t>
+          <t>D · Wünsche und Fairness</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Wie wird heute in LogX eingetragen? Hilfreich wären Bildschirmfotos und ein exportierter alter Plan.</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n"/>
+          <t>Wochenenden: reihum verteilen, oder hat jemand fest frei?</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Heute: reihum, so gleich wie möglich.</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="5" t="n">
@@ -1011,15 +1115,104 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Ablauf und LogX</t>
+          <t>D · Wünsche und Fairness</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Kann LogX Dateien importieren oder exportieren (Excel/CSV)? Gibt es eine Mitarbeiterliste zum Exportieren?</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n"/>
+          <t>Fällt jemand aus: nur die Lücke melden oder gleich vorschlagen, wen man fragen kann?</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Heute: bis zu drei Vorschläge.</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>E · Ablauf</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Wer erstellt und veröffentlicht den Plan – nur die Geschäftsführung oder auch die Studioleitung für ihr Studio?</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Heute: nur die Geschäftsführung.</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>E · Ablauf</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Bis wann muss der Plan für den nächsten Monat fertig sein (z. B. am 20.)?</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Heute: keine Frist.</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="n"/>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>E · Ablauf</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Muss die Leitung jeden Schichttausch bestätigen?</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Heute: ja.</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>E · Ablauf</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Wird der Plan danach noch in LogX eingetragen? (Was ich dafür brauche: letzte Seite)</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Heute: „Für LogX kopieren“ legt eine Tabelle in die Zwischenablage.</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1115,7 +1308,7 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Longerich</t>
         </is>
@@ -1132,7 +1325,7 @@
       <c r="K2" s="6" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Nippes</t>
         </is>
@@ -1149,7 +1342,7 @@
       <c r="K3" s="6" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Ebertplatz</t>
         </is>
@@ -1166,7 +1359,7 @@
       <c r="K4" s="6" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Rath</t>
         </is>
@@ -1183,7 +1376,7 @@
       <c r="K5" s="6" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Porz</t>
         </is>
@@ -1200,7 +1393,7 @@
       <c r="K6" s="6" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Rondorf</t>
         </is>
@@ -1217,7 +1410,7 @@
       <c r="K7" s="6" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Hürth</t>
         </is>
@@ -1234,7 +1427,7 @@
       <c r="K8" s="6" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Brühl</t>
         </is>
@@ -1251,7 +1444,7 @@
       <c r="K9" s="6" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Niederkassel Mondorf</t>
         </is>
@@ -1268,7 +1461,7 @@
       <c r="K10" s="6" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Refrath</t>
         </is>
@@ -1285,7 +1478,7 @@
       <c r="K11" s="6" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Overath</t>
         </is>
@@ -1302,7 +1495,7 @@
       <c r="K12" s="6" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Marialinden</t>
         </is>
@@ -1319,7 +1512,7 @@
       <c r="K13" s="6" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Rösrath</t>
         </is>
@@ -1336,7 +1529,7 @@
       <c r="K14" s="6" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Seelscheid</t>
         </is>
@@ -1353,7 +1546,7 @@
       <c r="K15" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Beispiel für eine Zeile: Mo 07:00–21:00 · mindestens 1 · „Mo–Do 16–20 Uhr 2 Personen“ · „Sa nur bis 14 Uhr“</t>
         </is>
@@ -1434,112 +1627,112 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>alle</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Früh</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>Mo–Fr</t>
         </is>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="F2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="10" t="inlineStr"/>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr"/>
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>Beispiel – bitte anpassen</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>alle</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Spät</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>Mo–Fr</t>
         </is>
       </c>
-      <c r="F3" s="10" t="n">
+      <c r="F3" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>Abschluss</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>Beispiel – bitte anpassen</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>alle</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Samstag</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Sa</t>
         </is>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="10" t="inlineStr"/>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr"/>
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>Beispiel – bitte anpassen</t>
         </is>
@@ -2079,194 +2272,194 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Beispiel: Lisa M.</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Minijob</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Nippes</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Longerich, Ebertplatz</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr"/>
-      <c r="F2" s="10" t="n">
+      <c r="E2" s="11" t="inlineStr"/>
+      <c r="F2" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="G2" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>Probetraining</t>
         </is>
       </c>
-      <c r="K2" s="10" t="inlineStr">
+      <c r="K2" s="11" t="inlineStr">
         <is>
           <t>nur spät</t>
         </is>
       </c>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="L2" s="11" t="inlineStr">
         <is>
           <t>nie</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr">
+      <c r="M2" s="11" t="inlineStr">
         <is>
           <t>nur spät</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr">
+      <c r="N2" s="11" t="inlineStr">
         <is>
           <t>nie</t>
         </is>
       </c>
-      <c r="O2" s="10" t="inlineStr">
+      <c r="O2" s="11" t="inlineStr">
         <is>
           <t>ganztags</t>
         </is>
       </c>
-      <c r="P2" s="10" t="inlineStr">
+      <c r="P2" s="11" t="inlineStr">
         <is>
           <t>ganztags</t>
         </is>
       </c>
-      <c r="Q2" s="10" t="inlineStr">
+      <c r="Q2" s="11" t="inlineStr">
         <is>
           <t>nie</t>
         </is>
       </c>
-      <c r="R2" s="10" t="inlineStr"/>
-      <c r="S2" s="10" t="inlineStr">
+      <c r="R2" s="11" t="inlineStr"/>
+      <c r="S2" s="11" t="inlineStr">
         <is>
           <t>Spät</t>
         </is>
       </c>
-      <c r="T2" s="10" t="inlineStr">
+      <c r="T2" s="11" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="U2" s="10" t="inlineStr"/>
-      <c r="V2" s="10" t="inlineStr"/>
-      <c r="W2" s="10" t="inlineStr">
+      <c r="U2" s="11" t="inlineStr"/>
+      <c r="V2" s="11" t="inlineStr"/>
+      <c r="W2" s="11" t="inlineStr">
         <is>
           <t>samstags nur alle zwei Wochen</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Beispiel: Tom K.</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Azubi</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Porz</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr"/>
-      <c r="E3" s="10" t="n">
+      <c r="D3" s="11" t="inlineStr"/>
+      <c r="E3" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="F3" s="10" t="inlineStr"/>
-      <c r="G3" s="10" t="n">
+      <c r="F3" s="11" t="inlineStr"/>
+      <c r="G3" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr"/>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr"/>
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t>ganztags</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="L3" s="11" t="inlineStr">
         <is>
           <t>nie</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr">
+      <c r="M3" s="11" t="inlineStr">
         <is>
           <t>ganztags</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr">
+      <c r="N3" s="11" t="inlineStr">
         <is>
           <t>ganztags</t>
         </is>
       </c>
-      <c r="O3" s="10" t="inlineStr">
+      <c r="O3" s="11" t="inlineStr">
         <is>
           <t>ganztags</t>
         </is>
       </c>
-      <c r="P3" s="10" t="inlineStr">
+      <c r="P3" s="11" t="inlineStr">
         <is>
           <t>nie</t>
         </is>
       </c>
-      <c r="Q3" s="10" t="inlineStr">
+      <c r="Q3" s="11" t="inlineStr">
         <is>
           <t>nie</t>
         </is>
       </c>
-      <c r="R3" s="10" t="inlineStr">
+      <c r="R3" s="11" t="inlineStr">
         <is>
           <t>Di Berufsschule</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="11" t="inlineStr">
         <is>
           <t>Früh</t>
         </is>
       </c>
-      <c r="T3" s="10" t="inlineStr">
+      <c r="T3" s="11" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="U3" s="10" t="inlineStr">
+      <c r="U3" s="11" t="inlineStr">
         <is>
           <t>01.11.2026</t>
         </is>
       </c>
-      <c r="V3" s="10" t="inlineStr"/>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="V3" s="11" t="inlineStr"/>
+      <c r="W3" s="11" t="inlineStr">
         <is>
           <t>nicht allein – immer mit Studioleitung</t>
         </is>
@@ -6020,54 +6213,54 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Lisa M.</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Nippes</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Spät</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Mo, Mi</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>Beispiel – bitte anpassen</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Tom K.</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Porz</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Früh</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>14.11.2026</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>Beispiel – Einweisung neues Gerät</t>
         </is>
@@ -6537,58 +6730,58 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>24.12.2026</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>alle</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>geschlossen</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Spät</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr"/>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Beispiel – Heiligabend nur bis 14 Uhr</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>07.11.2026</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Rath</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>mehr Personen</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>Samstag</t>
         </is>
       </c>
-      <c r="E3" s="10" t="n">
+      <c r="E3" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Beispiel – Tag der offenen Tür</t>
         </is>
@@ -7261,7 +7454,7 @@
           <t>Wunschfrist (Tag im Vormonat)</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="8" t="n">
         <v>15</v>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -7276,7 +7469,7 @@
           <t>Feiertage geschlossen?</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
@@ -7293,7 +7486,7 @@
           <t>Höchstens Tage am Stück</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -7308,7 +7501,7 @@
           <t>Höchstens Wunsch-frei-Tage pro Person und Monat</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
